--- a/PO_TBD_20260605.xlsx
+++ b/PO_TBD_20260605.xlsx
@@ -2536,7 +2536,7 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>TAB BELTAS (BILASTINE) 20MG GLENMARK</t>
+          <t>SYR SEDILIX-RX LINCTUS (DEXTROMETHORPHAN 15MG/ PROMETHAZINE 3.125MG/ PHENYLEPHRINE 5MG EVERY 5ML)  90ML XEPA</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
@@ -2546,20 +2546,20 @@
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="F70" s="5" t="n">
-        <v>100</v>
+        <v>11</v>
       </c>
       <c r="G70" s="7" t="n">
-        <v>0.798</v>
+        <v>5.9</v>
       </c>
       <c r="H70" s="7" t="n">
-        <v>79.8</v>
+        <v>64.90000000000001</v>
       </c>
     </row>
     <row r="71">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="B71" s="9" t="inlineStr">
         <is>
-          <t>TAB PARACAP 500MG HEALTH PHARM</t>
+          <t>TAB BELTAS (BILASTINE) 20MG GLENMARK</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
@@ -2582,16 +2582,16 @@
         </is>
       </c>
       <c r="E71" s="8" t="n">
-        <v>420</v>
+        <v>30</v>
       </c>
       <c r="F71" s="8" t="n">
-        <v>209</v>
+        <v>100</v>
       </c>
       <c r="G71" s="10" t="n">
-        <v>0.157</v>
+        <v>0.798</v>
       </c>
       <c r="H71" s="10" t="n">
-        <v>32.81</v>
+        <v>79.8</v>
       </c>
     </row>
     <row r="72">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>TAB MUCOSOLVAN (AMBROXOL) 30MG DKSH</t>
+          <t>TAB PARACAP 500MG HEALTH PHARM</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
@@ -2614,16 +2614,16 @@
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>60</v>
+        <v>410</v>
       </c>
       <c r="F72" s="5" t="n">
-        <v>124</v>
+        <v>229</v>
       </c>
       <c r="G72" s="7" t="n">
-        <v>0.459</v>
+        <v>0.157</v>
       </c>
       <c r="H72" s="7" t="n">
-        <v>56.92</v>
+        <v>35.95</v>
       </c>
     </row>
     <row r="73">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>TAB SPASIL (DIPHENOXYLATE 2.5MG/ATROPINE 0.025MG) IMEKS</t>
+          <t>TAB MUCOSOLVAN (AMBROXOL) 30MG DKSH</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
@@ -2646,16 +2646,16 @@
         </is>
       </c>
       <c r="E73" s="8" t="n">
-        <v>420</v>
+        <v>60</v>
       </c>
       <c r="F73" s="8" t="n">
-        <v>183</v>
+        <v>124</v>
       </c>
       <c r="G73" s="10" t="n">
-        <v>0.164</v>
+        <v>0.459</v>
       </c>
       <c r="H73" s="10" t="n">
-        <v>30.01</v>
+        <v>56.92</v>
       </c>
     </row>
     <row r="74">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>TAB CLARINASE (PSEUDOEPHEDRINE 120MG, LORATADINE 5MG) BAYER</t>
+          <t>TAB SPASIL (DIPHENOXYLATE 2.5MG/ATROPINE 0.025MG) IMEKS</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
@@ -2678,16 +2678,16 @@
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>210</v>
+        <v>400</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>167</v>
+        <v>223</v>
       </c>
       <c r="G74" s="7" t="n">
-        <v>1.814</v>
+        <v>0.164</v>
       </c>
       <c r="H74" s="7" t="n">
-        <v>302.94</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="75">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="B75" s="9" t="inlineStr">
         <is>
-          <t>EFF GRANULES AVOSODA (SODIUM BICARBONATE) 1.916G/SACHET ABIO</t>
+          <t>TAB CLARINASE (PSEUDOEPHEDRINE 120MG, LORATADINE 5MG) BAYER</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr">
@@ -2706,20 +2706,20 @@
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>SACHET</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E75" s="8" t="n">
-        <v>84</v>
+        <v>210</v>
       </c>
       <c r="F75" s="8" t="n">
-        <v>53</v>
+        <v>167</v>
       </c>
       <c r="G75" s="10" t="n">
-        <v>1.01</v>
+        <v>1.814</v>
       </c>
       <c r="H75" s="10" t="n">
-        <v>53.53</v>
+        <v>302.94</v>
       </c>
     </row>
     <row r="76">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>TABLET METGYL (METRONIDAZOLE) 400MG SM PHARMACEUTICALS</t>
+          <t>EFF GRANULES AVOSODA (SODIUM BICARBONATE) 1.916G/SACHET ABIO</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
@@ -2738,20 +2738,20 @@
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>SACHET</t>
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="F76" s="5" t="n">
-        <v>92</v>
+        <v>53</v>
       </c>
       <c r="G76" s="7" t="n">
-        <v>0.089</v>
+        <v>1.01</v>
       </c>
       <c r="H76" s="7" t="n">
-        <v>8.19</v>
+        <v>53.53</v>
       </c>
     </row>
     <row r="77">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="B77" s="9" t="inlineStr">
         <is>
-          <t>TAB NORCOLUT (NORETHISTERONE) 5MG PAHANG PHARMACY</t>
+          <t>TABLET METGYL (METRONIDAZOLE) 400MG SM PHARMACEUTICALS</t>
         </is>
       </c>
       <c r="C77" s="8" t="inlineStr">
@@ -2774,16 +2774,16 @@
         </is>
       </c>
       <c r="E77" s="8" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="F77" s="8" t="n">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="G77" s="10" t="n">
-        <v>0.5</v>
+        <v>0.089</v>
       </c>
       <c r="H77" s="10" t="n">
-        <v>10</v>
+        <v>8.19</v>
       </c>
     </row>
     <row r="78">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>TAB VOREN (DICLOFENAC SODIUM) 50MG Y.S.P.</t>
+          <t>TAB NORCOLUT (NORETHISTERONE) 5MG PAHANG PHARMACY</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
@@ -2806,16 +2806,16 @@
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G78" s="7" t="n">
-        <v>0.119</v>
+        <v>0.5</v>
       </c>
       <c r="H78" s="7" t="n">
-        <v>3.45</v>
+        <v>10</v>
       </c>
     </row>
     <row r="79">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="B79" s="9" t="inlineStr">
         <is>
-          <t>TAB IBUPROFEN 400MG Y.S.P.</t>
+          <t>TAB VOREN (DICLOFENAC SODIUM) 50MG Y.S.P.</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr">
@@ -2841,13 +2841,13 @@
         <v>90</v>
       </c>
       <c r="F79" s="8" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G79" s="10" t="n">
-        <v>0.203</v>
+        <v>0.119</v>
       </c>
       <c r="H79" s="10" t="n">
-        <v>7.11</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="80">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>TAB DUOFOLIC (FOLIC ACID) 5MG DUOPHARMA</t>
+          <t>TAB IBUPROFEN 400MG Y.S.P.</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
@@ -2870,16 +2870,16 @@
         </is>
       </c>
       <c r="E80" s="5" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="F80" s="5" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G80" s="7" t="n">
-        <v>0.065</v>
+        <v>0.203</v>
       </c>
       <c r="H80" s="7" t="n">
-        <v>1.62</v>
+        <v>7.11</v>
       </c>
     </row>
     <row r="81">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="B81" s="9" t="inlineStr">
         <is>
-          <t>TAB SHINTAMET (CIMETIDINE) 400MG Y.S.P.</t>
+          <t>TAB DUOFOLIC (FOLIC ACID) 5MG DUOPHARMA</t>
         </is>
       </c>
       <c r="C81" s="8" t="inlineStr">
@@ -2902,16 +2902,16 @@
         </is>
       </c>
       <c r="E81" s="8" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F81" s="8" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="G81" s="10" t="n">
-        <v>0.584</v>
+        <v>0.065</v>
       </c>
       <c r="H81" s="10" t="n">
-        <v>23.36</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="82">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>CAP LOMODIUM (LOPERAMIDE) 2MG DYNAPHARM</t>
+          <t>TAB SHINTAMET (CIMETIDINE) 400MG Y.S.P.</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
@@ -2934,16 +2934,16 @@
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F82" s="5" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="G82" s="7" t="n">
-        <v>0.093</v>
+        <v>0.584</v>
       </c>
       <c r="H82" s="7" t="n">
-        <v>1.67</v>
+        <v>23.36</v>
       </c>
     </row>
     <row r="83">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="B83" s="9" t="inlineStr">
         <is>
-          <t>SYR BUCANIL (TERBUTALINE SULPHATE 1.5MG/5ML) 100ML Y.S.P.</t>
+          <t>CAP LOMODIUM (LOPERAMIDE) 2MG DYNAPHARM</t>
         </is>
       </c>
       <c r="C83" s="8" t="inlineStr">
@@ -2962,20 +2962,20 @@
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E83" s="8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F83" s="8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G83" s="10" t="n">
-        <v>0</v>
+        <v>0.093</v>
       </c>
       <c r="H83" s="10" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="84">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>TAB DUPHASTON (DYDROGESTERONE) 10MG ABBOTT</t>
+          <t>SYR BUCANIL (TERBUTALINE SULPHATE 1.5MG/5ML) 100ML Y.S.P.</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
@@ -2994,20 +2994,20 @@
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F84" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G84" s="7" t="n">
-        <v>3.675</v>
+        <v>0</v>
       </c>
       <c r="H84" s="7" t="n">
-        <v>58.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="B85" s="9" t="inlineStr">
         <is>
-          <t>TAB HOVASC (AMLODIPINE) 5MG HOVID</t>
+          <t>TAB DUPHASTON (DYDROGESTERONE) 10MG ABBOTT</t>
         </is>
       </c>
       <c r="C85" s="8" t="inlineStr">
@@ -3030,16 +3030,16 @@
         </is>
       </c>
       <c r="E85" s="8" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="F85" s="8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G85" s="10" t="n">
-        <v>0.24</v>
+        <v>3.675</v>
       </c>
       <c r="H85" s="10" t="n">
-        <v>3.6</v>
+        <v>58.8</v>
       </c>
     </row>
     <row r="86">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>TAB HOVASC (AMLODIPINE) 10MG HOVID</t>
+          <t>TAB HOVASC (AMLODIPINE) 5MG HOVID</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
@@ -3062,16 +3062,16 @@
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F86" s="5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G86" s="7" t="n">
-        <v>0.35</v>
+        <v>0.24</v>
       </c>
       <c r="H86" s="7" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="87">
@@ -3080,7 +3080,7 @@
       </c>
       <c r="B87" s="9" t="inlineStr">
         <is>
-          <t>TAB NORMATEN (ATENOLOL) 50MG XEPA</t>
+          <t>TAB HOVASC (AMLODIPINE) 10MG HOVID</t>
         </is>
       </c>
       <c r="C87" s="8" t="inlineStr">
@@ -3094,16 +3094,16 @@
         </is>
       </c>
       <c r="E87" s="8" t="n">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="F87" s="8" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G87" s="10" t="n">
-        <v>0.26786</v>
+        <v>0.35</v>
       </c>
       <c r="H87" s="10" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="88">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>TAB DELTACARBON (CHARCOAL) 250MG IMEKS</t>
+          <t>TAB NORMATEN (ATENOLOL) 50MG XEPA</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
@@ -3126,16 +3126,16 @@
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="F88" s="5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G88" s="7" t="n">
-        <v>0.438</v>
+        <v>0.26786</v>
       </c>
       <c r="H88" s="7" t="n">
-        <v>6.57</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="89">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="B89" s="9" t="inlineStr">
         <is>
-          <t>TAB BETASERC (BETAHISTINE) 24MG ABBOTT</t>
+          <t>TAB DELTACARBON (CHARCOAL) 250MG IMEKS</t>
         </is>
       </c>
       <c r="C89" s="8" t="inlineStr">
@@ -3158,16 +3158,16 @@
         </is>
       </c>
       <c r="E89" s="8" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="F89" s="8" t="n">
         <v>15</v>
       </c>
       <c r="G89" s="10" t="n">
-        <v>1.617</v>
+        <v>0.438</v>
       </c>
       <c r="H89" s="10" t="n">
-        <v>24.25</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="90">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>TAB COPASTIN (CLOPERASTINE) 10MG Y.S.P.</t>
+          <t>TAB BETASERC (BETAHISTINE) 24MG ABBOTT</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
@@ -3190,16 +3190,16 @@
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G90" s="7" t="n">
-        <v>0.236</v>
+        <v>1.617</v>
       </c>
       <c r="H90" s="7" t="n">
-        <v>5.9</v>
+        <v>24.25</v>
       </c>
     </row>
     <row r="91">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="B91" s="9" t="inlineStr">
         <is>
-          <t>TAB CONCOR (BISOPROLOL) 5MG MERCKS</t>
+          <t>TAB COPASTIN (CLOPERASTINE) 10MG Y.S.P.</t>
         </is>
       </c>
       <c r="C91" s="8" t="inlineStr">
@@ -3222,16 +3222,16 @@
         </is>
       </c>
       <c r="E91" s="8" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F91" s="8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="G91" s="10" t="n">
-        <v>1.53</v>
+        <v>0.236</v>
       </c>
       <c r="H91" s="10" t="n">
-        <v>15.3</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="92">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>SMECTA (DIOSMECTITE 3G) ORANGE-VANILLA POWDER SACHETS ZUELLIG</t>
+          <t>TAB CONCOR (BISOPROLOL) 5MG MERCKS</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
@@ -3250,20 +3250,20 @@
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>SACHET</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F92" s="5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G92" s="7" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="H92" s="7" t="n">
-        <v>19.92</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="93">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="B93" s="9" t="inlineStr">
         <is>
-          <t>IVD N/S 0.9% 500ML B. BRAUN</t>
+          <t>SMECTA (DIOSMECTITE 3G) ORANGE-VANILLA POWDER SACHETS ZUELLIG</t>
         </is>
       </c>
       <c r="C93" s="8" t="inlineStr">
@@ -3282,20 +3282,20 @@
       </c>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>SACHET</t>
         </is>
       </c>
       <c r="E93" s="8" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F93" s="8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G93" s="10" t="n">
-        <v>3.628</v>
+        <v>1.66</v>
       </c>
       <c r="H93" s="10" t="n">
-        <v>47.16</v>
+        <v>19.92</v>
       </c>
     </row>
     <row r="94">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>TAB CAFFOX ( ERGOTAMINE TARTRATE 1MG + CAFFINE 100MG ) IMEKS</t>
+          <t>IVD N/S 0.9% 500ML B. BRAUN</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
@@ -3314,20 +3314,20 @@
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F94" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G94" s="7" t="n">
-        <v>0.73</v>
+        <v>3.628</v>
       </c>
       <c r="H94" s="7" t="n">
-        <v>10.22</v>
+        <v>47.16</v>
       </c>
     </row>
     <row r="95">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="B95" s="9" t="inlineStr">
         <is>
-          <t>TAB VELOXIN (MECLOZINE 25MG/PYRIDOXINE 50MG) PHARM-D</t>
+          <t>TAB CAFFOX ( ERGOTAMINE TARTRATE 1MG + CAFFINE 100MG ) IMEKS</t>
         </is>
       </c>
       <c r="C95" s="8" t="inlineStr">
@@ -3350,16 +3350,16 @@
         </is>
       </c>
       <c r="E95" s="8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F95" s="8" t="n">
         <v>14</v>
       </c>
       <c r="G95" s="10" t="n">
-        <v>1.06</v>
+        <v>0.73</v>
       </c>
       <c r="H95" s="10" t="n">
-        <v>14.84</v>
+        <v>10.22</v>
       </c>
     </row>
     <row r="96">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>TAB LORADINE (LORATIDINE)10MG Y.S.P.</t>
+          <t>TAB VELOXIN (MECLOZINE 25MG/PYRIDOXINE 50MG) PHARM-D</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
@@ -3382,16 +3382,16 @@
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="F96" s="5" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G96" s="7" t="n">
-        <v>0.232</v>
+        <v>1.06</v>
       </c>
       <c r="H96" s="7" t="n">
-        <v>5.8</v>
+        <v>14.84</v>
       </c>
     </row>
     <row r="97">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="B97" s="9" t="inlineStr">
         <is>
-          <t>TAB NUELIN SR (THEOPHYLLINE) 250MG INOVA</t>
+          <t>TAB LORADINE (LORATIDINE)10MG Y.S.P.</t>
         </is>
       </c>
       <c r="C97" s="8" t="inlineStr">
@@ -3414,16 +3414,16 @@
         </is>
       </c>
       <c r="E97" s="8" t="n">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="F97" s="8" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="G97" s="10" t="n">
-        <v>0.78</v>
+        <v>0.232</v>
       </c>
       <c r="H97" s="10" t="n">
-        <v>10.14</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="98">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>TAB DULCOLAX ( BISACODYL ) 5MG SANOFI</t>
+          <t>TAB NUELIN SR (THEOPHYLLINE) 250MG INOVA</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
@@ -3449,13 +3449,13 @@
         <v>20</v>
       </c>
       <c r="F98" s="5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G98" s="7" t="n">
-        <v>0.265</v>
+        <v>0.78</v>
       </c>
       <c r="H98" s="7" t="n">
-        <v>3.98</v>
+        <v>10.14</v>
       </c>
     </row>
     <row r="99">
@@ -3464,7 +3464,7 @@
       </c>
       <c r="B99" s="9" t="inlineStr">
         <is>
-          <t>TAB STORVAS C (ATORVASTATIN) 20MG RANBAXY</t>
+          <t>TAB DULCOLAX ( BISACODYL ) 5MG SANOFI</t>
         </is>
       </c>
       <c r="C99" s="8" t="inlineStr">
@@ -3481,13 +3481,13 @@
         <v>20</v>
       </c>
       <c r="F99" s="8" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="G99" s="10" t="n">
-        <v>0.68</v>
+        <v>0.265</v>
       </c>
       <c r="H99" s="10" t="n">
-        <v>27.2</v>
+        <v>3.98</v>
       </c>
     </row>
     <row r="100">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>TAB DIAPO (DIAZEPAM) 5MG DUOPHARMA</t>
+          <t>TAB STORVAS C (ATORVASTATIN) 20MG RANBAXY</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
@@ -3510,16 +3510,16 @@
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F100" s="5" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="G100" s="7" t="n">
-        <v>1.44</v>
+        <v>0.68</v>
       </c>
       <c r="H100" s="7" t="n">
-        <v>14.4</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="101">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="B101" s="9" t="inlineStr">
         <is>
-          <t>APPETON A-Z VITAMIN C 30MG PASTILLES 5'S</t>
+          <t>TAB DIAPO (DIAZEPAM) 5MG DUOPHARMA</t>
         </is>
       </c>
       <c r="C101" s="8" t="inlineStr">
@@ -3538,20 +3538,20 @@
       </c>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>BOX</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E101" s="8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F101" s="8" t="n">
         <v>10</v>
       </c>
       <c r="G101" s="10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="H101" s="10" t="n">
-        <v>0</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="102">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>TAB ZITHROLIDE (AZITHROMYCIN)  500MG PHARMANIAGA</t>
+          <t>APPETON A-Z VITAMIN C 30MG PASTILLES 5'S</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
@@ -3570,20 +3570,20 @@
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>PACKET</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="E102" s="5" t="n">
         <v>7</v>
       </c>
       <c r="F102" s="5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G102" s="7" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="H102" s="7" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="B103" s="9" t="inlineStr">
         <is>
-          <t>INJ PIRIMAT (CHLORPHENIRAMINE) 10MG/ML DUOPHARMA</t>
+          <t>TAB ZITHROLIDE (AZITHROMYCIN)  500MG PHARMANIAGA</t>
         </is>
       </c>
       <c r="C103" s="8" t="inlineStr">
@@ -3602,20 +3602,20 @@
       </c>
       <c r="D103" s="8" t="inlineStr">
         <is>
-          <t>VIAL</t>
+          <t>PACKET</t>
         </is>
       </c>
       <c r="E103" s="8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F103" s="8" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G103" s="10" t="n">
-        <v>1.75</v>
+        <v>5.5</v>
       </c>
       <c r="H103" s="10" t="n">
-        <v>17.5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="104">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>NEBULE VENTOLIN (SALBUTAMOL) 2.5MG/2.5ML GSK</t>
+          <t>INJ PIRIMAT (CHLORPHENIRAMINE) 10MG/ML DUOPHARMA</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
@@ -3634,20 +3634,20 @@
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>RESPULE</t>
+          <t>VIAL</t>
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F104" s="5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G104" s="7" t="n">
-        <v>4.82</v>
+        <v>1.75</v>
       </c>
       <c r="H104" s="7" t="n">
-        <v>24.1</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="105">
@@ -3656,7 +3656,7 @@
       </c>
       <c r="B105" s="9" t="inlineStr">
         <is>
-          <t>SYR RETORIN (ERYTHROMYCIN) 200MG/5ML 60ML SM PHARMA</t>
+          <t>NEBULE VENTOLIN (SALBUTAMOL) 2.5MG/2.5ML GSK</t>
         </is>
       </c>
       <c r="C105" s="8" t="inlineStr">
@@ -3666,20 +3666,20 @@
       </c>
       <c r="D105" s="8" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>RESPULE</t>
         </is>
       </c>
       <c r="E105" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="F105" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F105" s="8" t="n">
-        <v>9</v>
-      </c>
       <c r="G105" s="10" t="n">
-        <v>4</v>
+        <v>4.82</v>
       </c>
       <c r="H105" s="10" t="n">
-        <v>36</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="106">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>SUPP VOREN (DICLOFENAC SODIUM) 25MG Y.S.P.</t>
+          <t>SYR RETORIN (ERYTHROMYCIN) 200MG/5ML 60ML SM PHARMA</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
@@ -3698,20 +3698,20 @@
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>SUPPOSITORIES</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F106" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="G106" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="G106" s="7" t="n">
-        <v>1.66</v>
-      </c>
       <c r="H106" s="7" t="n">
-        <v>6.64</v>
+        <v>36</v>
       </c>
     </row>
     <row r="107">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="B107" s="9" t="inlineStr">
         <is>
-          <t>SUPP VOREN (DICLOFENAC SODIUM) 50MG Y.S.P.</t>
+          <t>SUPP VOREN (DICLOFENAC SODIUM) 25MG Y.S.P.</t>
         </is>
       </c>
       <c r="C107" s="8" t="inlineStr">
@@ -3734,16 +3734,16 @@
         </is>
       </c>
       <c r="E107" s="8" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F107" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G107" s="10" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="H107" s="10" t="n">
-        <v>1.59</v>
+        <v>6.64</v>
       </c>
     </row>
     <row r="108">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>CAP BIOZOLE (FLUCANAZOLE) 150MG MEDISPEC</t>
+          <t>SUPP VOREN (DICLOFENAC SODIUM) 50MG Y.S.P.</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
@@ -3762,20 +3762,20 @@
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>SUPPOSITORIES</t>
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F108" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G108" s="7" t="n">
-        <v>4.91</v>
+        <v>1.59</v>
       </c>
       <c r="H108" s="7" t="n">
-        <v>24.55</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="109">
@@ -3784,7 +3784,7 @@
       </c>
       <c r="B109" s="9" t="inlineStr">
         <is>
-          <t>CANDID-B ( CLOTRIMAZOLE 1%W/W /BECLOMETHASONE 0.025%W/W ) CREAM 15G Y.S.P.</t>
+          <t>CAP BIOZOLE (FLUCANAZOLE) 150MG MEDISPEC</t>
         </is>
       </c>
       <c r="C109" s="8" t="inlineStr">
@@ -3794,20 +3794,20 @@
       </c>
       <c r="D109" s="8" t="inlineStr">
         <is>
-          <t>TUBE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E109" s="8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F109" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G109" s="10" t="n">
-        <v>12.33</v>
+        <v>4.91</v>
       </c>
       <c r="H109" s="10" t="n">
-        <v>12.33</v>
+        <v>24.55</v>
       </c>
     </row>
     <row r="110">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>CANDID EARDROPS (CLOTRIMAZOLE 1%) 15ML GLENMARK</t>
+          <t>CANDID-B ( CLOTRIMAZOLE 1%W/W /BECLOMETHASONE 0.025%W/W ) CREAM 15G Y.S.P.</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
@@ -3826,20 +3826,20 @@
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>TUBE</t>
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F110" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G110" s="7" t="n">
-        <v>18.95</v>
+        <v>12.33</v>
       </c>
       <c r="H110" s="7" t="n">
-        <v>18.95</v>
+        <v>12.33</v>
       </c>
     </row>
     <row r="111">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="B111" s="9" t="inlineStr">
         <is>
-          <t>INJ METHYCOBAL (MECOBALAMIN B12) 500MCG 1ML VIAL EISAI</t>
+          <t>CANDID EARDROPS (CLOTRIMAZOLE 1%) 15ML GLENMARK</t>
         </is>
       </c>
       <c r="C111" s="8" t="inlineStr">
@@ -3858,20 +3858,20 @@
       </c>
       <c r="D111" s="8" t="inlineStr">
         <is>
-          <t>VIAL</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E111" s="8" t="n">
         <v>4</v>
       </c>
       <c r="F111" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G111" s="10" t="n">
-        <v>6.8</v>
+        <v>18.95</v>
       </c>
       <c r="H111" s="10" t="n">
-        <v>27.2</v>
+        <v>18.95</v>
       </c>
     </row>
     <row r="112">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>SYR LACTUL (LACTULOSE 670MG/ML) 100ML Y.S.P.</t>
+          <t>INJ METHYCOBAL (MECOBALAMIN B12) 500MCG 1ML VIAL EISAI</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
@@ -3890,20 +3890,20 @@
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>VIAL</t>
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F112" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G112" s="7" t="n">
-        <v>10</v>
+        <v>6.8</v>
       </c>
       <c r="H112" s="7" t="n">
-        <v>20</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="113">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="B113" s="9" t="inlineStr">
         <is>
-          <t>SYR COLIMIX (DICYCLOMINE 5MG/ SIMETHICONE 50MG) 90ML XEPA</t>
+          <t>SYR LACTUL (LACTULOSE 670MG/ML) 100ML Y.S.P.</t>
         </is>
       </c>
       <c r="C113" s="8" t="inlineStr">
@@ -3926,16 +3926,16 @@
         </is>
       </c>
       <c r="E113" s="8" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F113" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G113" s="10" t="n">
-        <v>7.55</v>
+        <v>10</v>
       </c>
       <c r="H113" s="10" t="n">
-        <v>15.1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="114">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>MDI VENTOLIN EVOHALER (SALBUTAMOL 100MCG) GSK</t>
+          <t>SYR COLIMIX (DICYCLOMINE 5MG/ SIMETHICONE 50MG) 90ML XEPA</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
@@ -3954,20 +3954,20 @@
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>BOX</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F114" s="5" t="n">
         <v>2</v>
       </c>
       <c r="G114" s="7" t="n">
-        <v>26.1</v>
+        <v>7.55</v>
       </c>
       <c r="H114" s="7" t="n">
-        <v>52.2</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="115">
@@ -3976,7 +3976,7 @@
       </c>
       <c r="B115" s="9" t="inlineStr">
         <is>
-          <t>INJ SHINCORT (TRIAMCINOLONE ACETONIDE 40MG/ML) 1ML VIAL Y.S.P.</t>
+          <t>MDI VENTOLIN EVOHALER (SALBUTAMOL 100MCG) GSK</t>
         </is>
       </c>
       <c r="C115" s="8" t="inlineStr">
@@ -3986,20 +3986,20 @@
       </c>
       <c r="D115" s="8" t="inlineStr">
         <is>
-          <t>VIAL</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="E115" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F115" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G115" s="10" t="n">
-        <v>8.15</v>
+        <v>26.1</v>
       </c>
       <c r="H115" s="10" t="n">
-        <v>32.6</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="116">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>SYR FUCON (HYOSCINE-N-BUTYLBROMIDE) 1MG/ML 60ML Y.S.P.</t>
+          <t>INJ SHINCORT (TRIAMCINOLONE ACETONIDE 40MG/ML) 1ML VIAL Y.S.P.</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
@@ -4018,20 +4018,20 @@
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>VIAL</t>
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F116" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G116" s="7" t="n">
-        <v>7.05</v>
+        <v>8.15</v>
       </c>
       <c r="H116" s="7" t="n">
-        <v>14.1</v>
+        <v>32.6</v>
       </c>
     </row>
     <row r="117">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="B117" s="9" t="inlineStr">
         <is>
-          <t>NASAL DROPS ILIADIN 0.01% (OXYMETHAZOLINE) DECONGESTANT (&lt; 12MTHS ) P&amp;G</t>
+          <t>SYR FUCON (HYOSCINE-N-BUTYLBROMIDE) 1MG/ML 60ML Y.S.P.</t>
         </is>
       </c>
       <c r="C117" s="8" t="inlineStr">
@@ -4060,10 +4060,10 @@
         <v>2</v>
       </c>
       <c r="G117" s="10" t="n">
-        <v>16.56</v>
+        <v>7.05</v>
       </c>
       <c r="H117" s="10" t="n">
-        <v>33.12</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="118">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>DIFFLAM FORTE THROAT SPRAY  (BENZYDAMINE 0.3% W/V) ADULTS &amp; CHILD (&gt;6YRS) INOVA</t>
+          <t>NASAL DROPS ILIADIN 0.01% (OXYMETHAZOLINE) DECONGESTANT (&lt; 12MTHS ) P&amp;G</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
@@ -4086,16 +4086,16 @@
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F118" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G118" s="7" t="n">
-        <v>32</v>
+        <v>16.56</v>
       </c>
       <c r="H118" s="7" t="n">
-        <v>160</v>
+        <v>33.12</v>
       </c>
     </row>
     <row r="119">
@@ -4104,7 +4104,7 @@
       </c>
       <c r="B119" s="9" t="inlineStr">
         <is>
-          <t>EYE/EAR DROPS DEXTRACIN (DEXAMETHASONE &amp; NEOMYCIN) XEPA</t>
+          <t>DIFFLAM FORTE THROAT SPRAY  (BENZYDAMINE 0.3% W/V) ADULTS &amp; CHILD (&gt;6YRS) INOVA</t>
         </is>
       </c>
       <c r="C119" s="8" t="inlineStr">
@@ -4118,16 +4118,16 @@
         </is>
       </c>
       <c r="E119" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F119" s="8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G119" s="10" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="H119" s="10" t="n">
-        <v>20</v>
+        <v>224</v>
       </c>
     </row>
     <row r="120">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>INJ NON-PREG (MEDROXYPROGESTERONE ACETATE IM 150MG/3ML) VIAL HEALOL PHARMA</t>
+          <t>EYE/EAR DROPS DEXTRACIN (DEXAMETHASONE &amp; NEOMYCIN) XEPA</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
@@ -4146,20 +4146,20 @@
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>VIAL</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F120" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G120" s="7" t="n">
-        <v>8.800000000000001</v>
+        <v>5</v>
       </c>
       <c r="H120" s="7" t="n">
-        <v>8.800000000000001</v>
+        <v>25</v>
       </c>
     </row>
     <row r="121">
@@ -4168,7 +4168,7 @@
       </c>
       <c r="B121" s="9" t="inlineStr">
         <is>
-          <t>TAB ESCAPELLE (LEVONORGESTREL) 1.5MG 1'S PAHANG PHARMACY</t>
+          <t>INJ NON-PREG (MEDROXYPROGESTERONE ACETATE IM 150MG/3ML) VIAL HEALOL PHARMA</t>
         </is>
       </c>
       <c r="C121" s="8" t="inlineStr">
@@ -4178,20 +4178,20 @@
       </c>
       <c r="D121" s="8" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>VIAL</t>
         </is>
       </c>
       <c r="E121" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F121" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G121" s="10" t="n">
-        <v>12.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H121" s="10" t="n">
-        <v>25</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="122">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>TAB SYNFLEX (NAPROXEN SODIUM) 550MG DKSH</t>
+          <t>TAB ESCAPELLE (LEVONORGESTREL) 1.5MG 1'S PAHANG PHARMACY</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
@@ -4214,16 +4214,16 @@
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F122" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G122" s="7" t="n">
-        <v>1.414</v>
+        <v>12.5</v>
       </c>
       <c r="H122" s="7" t="n">
-        <v>7.07</v>
+        <v>25</v>
       </c>
     </row>
     <row r="123">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="B123" s="9" t="inlineStr">
         <is>
-          <t>SYRUP NOVOMIN (DIMENHYDRINATE) 15MG/5ML 60ML (ORANGE FLV) XEPA</t>
+          <t>TAB SYNFLEX (NAPROXEN SODIUM) 550MG DKSH</t>
         </is>
       </c>
       <c r="C123" s="8" t="inlineStr">
@@ -4242,20 +4242,20 @@
       </c>
       <c r="D123" s="8" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E123" s="8" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="F123" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G123" s="10" t="n">
-        <v>5.5</v>
+        <v>1.414</v>
       </c>
       <c r="H123" s="10" t="n">
-        <v>16.5</v>
+        <v>7.07</v>
       </c>
     </row>
     <row r="124">
@@ -4264,7 +4264,7 @@
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>VOREN (DICLOFENAC SODIUM 1%W/W) GEL PLUS 20G Y.SP.</t>
+          <t>SYRUP NOVOMIN (DIMENHYDRINATE) 15MG/5ML 60ML (ORANGE FLV) XEPA</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
@@ -4274,20 +4274,20 @@
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>TUBE</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F124" s="5" t="n">
         <v>3</v>
       </c>
       <c r="G124" s="7" t="n">
-        <v>9</v>
+        <v>5.5</v>
       </c>
       <c r="H124" s="7" t="n">
-        <v>27</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="125">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="B125" s="9" t="inlineStr">
         <is>
-          <t>TAB ZENTEL (ALBENDAZOLE) 200MG 2'S HALEON</t>
+          <t>VOREN (DICLOFENAC SODIUM 1%W/W) GEL PLUS 20G Y.SP.</t>
         </is>
       </c>
       <c r="C125" s="8" t="inlineStr">
@@ -4306,20 +4306,20 @@
       </c>
       <c r="D125" s="8" t="inlineStr">
         <is>
-          <t>PACKET</t>
+          <t>TUBE</t>
         </is>
       </c>
       <c r="E125" s="8" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F125" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G125" s="10" t="n">
-        <v>9.65</v>
+        <v>9</v>
       </c>
       <c r="H125" s="10" t="n">
-        <v>19.3</v>
+        <v>27</v>
       </c>
     </row>
     <row r="126">
@@ -4328,7 +4328,7 @@
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>SYR SEDILIX-RX LINCTUS (DEXTROMETHORPHAN 15MG/ PROMETHAZINE 3.125MG/ PHENYLEPHRINE 5MG EVERY 5ML)  90ML XEPA</t>
+          <t>TAB ZENTEL (ALBENDAZOLE) 200MG 2'S HALEON</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
@@ -4338,20 +4338,20 @@
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>PACKET</t>
         </is>
       </c>
       <c r="E126" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F126" s="5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G126" s="7" t="n">
-        <v>5.9</v>
+        <v>9.65</v>
       </c>
       <c r="H126" s="7" t="n">
-        <v>53.1</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="127">
@@ -4790,16 +4790,16 @@
         </is>
       </c>
       <c r="E140" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F140" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G140" s="7" t="n">
         <v>2.8</v>
       </c>
       <c r="H140" s="7" t="n">
-        <v>2.8</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="141">
@@ -5161,7 +5161,7 @@
         </is>
       </c>
       <c r="H152" s="12" t="n">
-        <v>5760.370000000002</v>
+        <v>5859.27</v>
       </c>
     </row>
     <row r="154">
@@ -5174,7 +5174,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-05 08:03</t>
+          <t>Generated: 2026-06-05 19:26</t>
         </is>
       </c>
     </row>
